--- a/outputs_xlsx_solution/test_new3.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.1-wide.xlsx
@@ -59,13 +59,16 @@
     <t>addi X2, X0, 5</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>addi X3, X0, 0</t>
   </si>
   <si>
-    <t>WB/CT</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>addi X4, X0, 4</t>
@@ -83,12 +86,12 @@
     <t>fmul F3, F3, F1</t>
   </si>
   <si>
-    <t>EX</t>
-  </si>
-  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>fadd F4, F4, F1</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
     <t>slt X5, X3, X2</t>
   </si>
   <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
     <t>bne X5, X0, 36</t>
   </si>
   <si>
@@ -125,13 +131,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -675,6 +699,12 @@
       <c r="BJ1">
         <v>59</v>
       </c>
+      <c r="BK1">
+        <v>60</v>
+      </c>
+      <c r="BL1">
+        <v>61</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -696,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -719,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -753,7 +783,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -765,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -776,7 +806,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -788,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -799,7 +829,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>5</v>
@@ -811,13 +841,13 @@
         <v>8</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -828,7 +858,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>5</v>
@@ -840,13 +870,13 @@
         <v>8</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -857,7 +887,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -866,34 +896,34 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="W9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -916,16 +946,16 @@
         <v>8</v>
       </c>
       <c r="O10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="s">
         <v>10</v>
       </c>
-      <c r="W10" t="s">
-        <v>10</v>
+      <c r="X10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -936,7 +966,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
         <v>5</v>
@@ -945,25 +975,25 @@
         <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U11" t="s">
         <v>10</v>
       </c>
-      <c r="W11" t="s">
-        <v>10</v>
+      <c r="Y11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -974,7 +1004,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N12" t="s">
         <v>5</v>
@@ -983,22 +1013,22 @@
         <v>6</v>
       </c>
       <c r="P12" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="X12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1009,7 +1039,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O13" t="s">
         <v>5</v>
@@ -1018,16 +1048,22 @@
         <v>6</v>
       </c>
       <c r="Q13" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="W13" t="s">
+        <v>24</v>
+      </c>
+      <c r="X13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1038,7 +1074,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
         <v>5</v>
@@ -1052,8 +1088,8 @@
       <c r="S14" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" t="s">
-        <v>10</v>
+      <c r="AC14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1064,7 +1100,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="s">
         <v>5</v>
@@ -1078,8 +1114,8 @@
       <c r="T15" t="s">
         <v>10</v>
       </c>
-      <c r="AA15" t="s">
-        <v>10</v>
+      <c r="AD15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1126,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R16" t="s">
         <v>5</v>
@@ -1099,16 +1135,16 @@
         <v>6</v>
       </c>
       <c r="T16" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V16" t="s">
         <v>10</v>
       </c>
-      <c r="AA16" t="s">
-        <v>10</v>
+      <c r="AE16" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1119,7 +1155,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S17" t="s">
         <v>5</v>
@@ -1128,16 +1164,16 @@
         <v>6</v>
       </c>
       <c r="U17" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V17" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W17" t="s">
         <v>10</v>
       </c>
-      <c r="AA17" t="s">
-        <v>10</v>
+      <c r="AF17" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1184,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W18" t="s">
         <v>5</v>
@@ -1160,13 +1196,16 @@
         <v>8</v>
       </c>
       <c r="Z18" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="s">
         <v>10</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1177,7 +1216,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X19" t="s">
         <v>5</v>
@@ -1186,22 +1225,31 @@
         <v>6</v>
       </c>
       <c r="Z19" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -1212,7 +1260,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s">
         <v>5</v>
@@ -1221,16 +1269,16 @@
         <v>6</v>
       </c>
       <c r="AA20" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AB20" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="s">
         <v>10</v>
       </c>
-      <c r="AE20" t="s">
-        <v>10</v>
+      <c r="AI20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1241,7 +1289,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s">
         <v>5</v>
@@ -1250,13 +1298,16 @@
         <v>6</v>
       </c>
       <c r="AB21" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AC21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -1267,7 +1318,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="s">
         <v>5</v>
@@ -1276,13 +1327,16 @@
         <v>6</v>
       </c>
       <c r="AC22" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AD22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="s">
         <v>10</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1293,7 +1347,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB23" t="s">
         <v>5</v>
@@ -1302,149 +1356,185 @@
         <v>6</v>
       </c>
       <c r="AD23" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="s">
         <v>10</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>5</v>
       </c>
       <c r="AD24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="s">
         <v>8</v>
       </c>
       <c r="AG24" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>5</v>
       </c>
       <c r="AE25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF25" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="s">
         <v>8</v>
       </c>
       <c r="AH25" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AI25" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>5</v>
       </c>
       <c r="AF26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="s">
         <v>8</v>
       </c>
       <c r="AI26" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>8</v>
       </c>
       <c r="AL26" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
       </c>
+      <c r="AF27" t="s">
+        <v>5</v>
+      </c>
       <c r="AG27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>24</v>
       </c>
       <c r="AL27" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="AG28" t="s">
+        <v>5</v>
+      </c>
       <c r="AH28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AJ28" t="s">
         <v>8</v>
@@ -1452,315 +1542,357 @@
       <c r="AK28" t="s">
         <v>10</v>
       </c>
-      <c r="AL28" t="s">
-        <v>10</v>
+      <c r="AQ28" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
       </c>
+      <c r="AH29" t="s">
+        <v>5</v>
+      </c>
       <c r="AI29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ29" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="s">
         <v>8</v>
       </c>
       <c r="AL29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM29" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>6</v>
       </c>
       <c r="AK30" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AL30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM30" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP30" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>6</v>
       </c>
       <c r="AL31" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AR31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
       </c>
+      <c r="AK32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>6</v>
+      </c>
       <c r="AM32" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AN32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO32" t="s">
         <v>8</v>
       </c>
       <c r="AP32" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AQ32" t="s">
         <v>10</v>
       </c>
-      <c r="AS32" t="s">
-        <v>10</v>
+      <c r="AU32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>6</v>
       </c>
       <c r="AN33" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AO33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP33" t="s">
         <v>8</v>
       </c>
       <c r="AQ33" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>8</v>
       </c>
       <c r="AS33" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>6</v>
       </c>
       <c r="AO34" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AQ34" t="s">
         <v>8</v>
       </c>
       <c r="AR34" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AS34" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU34" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW34" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>6</v>
       </c>
       <c r="AP35" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AQ35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR35" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>16</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ36" t="s">
         <v>18</v>
       </c>
       <c r="AR36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS36" t="s">
-        <v>6</v>
-      </c>
-      <c r="AT36" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AW36" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AY36" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>18</v>
       </c>
       <c r="AS37" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT37" t="s">
-        <v>6</v>
-      </c>
-      <c r="AU37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV37" t="s">
-        <v>16</v>
-      </c>
-      <c r="AW37" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX37" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY37" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>18</v>
       </c>
       <c r="AT38" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AU38" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV38" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW38" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX38" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ38" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BA38" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>18</v>
       </c>
       <c r="AU39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW39" t="s">
         <v>8</v>
@@ -1768,247 +1900,403 @@
       <c r="AX39" t="s">
         <v>10</v>
       </c>
-      <c r="AZ39" t="s">
-        <v>10</v>
+      <c r="BB39" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="AS40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>18</v>
       </c>
       <c r="AV40" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX40" t="s">
         <v>8</v>
       </c>
       <c r="AY40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ40" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="BA40" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB40" t="s">
+        <v>10</v>
+      </c>
+      <c r="BC40" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="AW41" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="AT41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>18</v>
       </c>
       <c r="AX41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY41" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AZ41" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BA41" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="BB41" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC41" t="s">
+        <v>10</v>
+      </c>
+      <c r="BD41" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>18</v>
       </c>
       <c r="AX42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY42" t="s">
-        <v>6</v>
-      </c>
-      <c r="AZ42" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA42" t="s">
-        <v>16</v>
-      </c>
-      <c r="BB42" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BE42" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="BB43" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC43" t="s">
-        <v>6</v>
-      </c>
-      <c r="BD43" t="s">
-        <v>8</v>
-      </c>
-      <c r="BE43" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>18</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ43" t="s">
+        <v>10</v>
       </c>
       <c r="BF43" t="s">
-        <v>16</v>
-      </c>
-      <c r="BG43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
-      </c>
-      <c r="BC44" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD44" t="s">
-        <v>6</v>
-      </c>
-      <c r="BE44" t="s">
-        <v>8</v>
-      </c>
-      <c r="BF44" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="AW44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ44" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA44" t="s">
+        <v>10</v>
       </c>
       <c r="BG44" t="s">
-        <v>16</v>
-      </c>
-      <c r="BH44" t="s">
-        <v>16</v>
-      </c>
-      <c r="BI44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
       </c>
-      <c r="BD45" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE45" t="s">
-        <v>6</v>
-      </c>
-      <c r="BF45" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG45" t="s">
-        <v>16</v>
+      <c r="AX45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ45" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA45" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB45" t="s">
+        <v>10</v>
       </c>
       <c r="BH45" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
       </c>
+      <c r="BB46" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC46" t="s">
+        <v>6</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>8</v>
+      </c>
       <c r="BE46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF46" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BI46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
         <v>16</v>
       </c>
-      <c r="BJ46" t="s">
-        <v>10</v>
+      <c r="BC47" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD47" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>8</v>
+      </c>
+      <c r="BF47" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG47" t="s">
+        <v>8</v>
+      </c>
+      <c r="BH47" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI47" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ47" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
         <v>27</v>
       </c>
+      <c r="BD48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE48" t="s">
+        <v>6</v>
+      </c>
+      <c r="BF48" t="s">
+        <v>18</v>
+      </c>
+      <c r="BG48" t="s">
+        <v>8</v>
+      </c>
+      <c r="BH48" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK48" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>76</v>
+      </c>
+      <c r="C49" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
+      <c r="BE49" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF49" t="s">
+        <v>6</v>
+      </c>
+      <c r="BG49" t="s">
+        <v>18</v>
+      </c>
+      <c r="BI49" t="s">
+        <v>8</v>
+      </c>
+      <c r="BJ49" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL49" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_new3.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.1-wide.xlsx
@@ -156,6 +156,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -2293,10 +2299,26 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
